--- a/measurements/36/Filled_2D_sections/sagittal/week36_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/36/Filled_2D_sections/sagittal/week36_sagittal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AA27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,72 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,43 +566,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10.8227245687091</v>
+        <v>4125.396825396825</v>
       </c>
       <c r="D2" t="n">
-        <v>19.54577456451044</v>
+        <v>381.6079795928228</v>
       </c>
       <c r="E2" t="n">
-        <v>14.24670210698756</v>
+        <v>278.1498982792809</v>
       </c>
       <c r="F2" t="n">
         <v>1.371950814843237</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3559923777161611</v>
+        <v>0.3559923777161612</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5236280487804879</v>
+        <v>1.42671130952381</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6473894817073171</v>
+        <v>12.63950892857143</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5855087652439025</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>5.093625992063491</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>7</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4.905133928571428</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>12.63950892857143</v>
+      </c>
+      <c r="R2" t="n">
+        <v>8.085140306122449</v>
+      </c>
+      <c r="S2" t="n">
+        <v>8</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.42671130952381</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.614211309523809</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2.476050967261905</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>10.70252825698989</v>
+      <c r="AA2" s="2" t="n">
+        <v>4079.580498866213</v>
       </c>
     </row>
     <row r="3">
@@ -553,43 +643,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10.8227245687091</v>
+        <v>4125.396825396825</v>
       </c>
       <c r="D3" t="n">
-        <v>19.54577456451044</v>
+        <v>381.6079795928228</v>
       </c>
       <c r="E3" t="n">
-        <v>14.24670210698756</v>
+        <v>278.1498982792809</v>
       </c>
       <c r="F3" t="n">
         <v>1.371950814843237</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3559923777161611</v>
+        <v>0.3559923777161612</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5236280487804879</v>
+        <v>1.42671130952381</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6473894817073171</v>
+        <v>12.63950892857143</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5855087652439025</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>5.093625992063491</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>7</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4.905133928571428</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>12.63950892857143</v>
+      </c>
+      <c r="R3" t="n">
+        <v>8.085140306122449</v>
+      </c>
+      <c r="S3" t="n">
+        <v>8</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.42671130952381</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.614211309523809</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2.476050967261905</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>19.57464395383509</v>
+      <c r="AA3" s="2" t="n">
+        <v>382.171620051066</v>
       </c>
     </row>
     <row r="4">
@@ -600,43 +720,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10.8227245687091</v>
+        <v>4125.396825396825</v>
       </c>
       <c r="D4" t="n">
-        <v>19.54577456451044</v>
+        <v>381.6079795928228</v>
       </c>
       <c r="E4" t="n">
-        <v>14.24670210698756</v>
+        <v>278.1498982792809</v>
       </c>
       <c r="F4" t="n">
         <v>1.371950814843237</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3559923777161611</v>
+        <v>0.3559923777161612</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5236280487804879</v>
+        <v>1.42671130952381</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6473894817073171</v>
+        <v>12.63950892857143</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5855087652439025</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>5.093625992063491</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>7</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.905133928571428</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>12.63950892857143</v>
+      </c>
+      <c r="R4" t="n">
+        <v>8.085140306122449</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.42671130952381</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.614211309523809</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.476050967261905</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>14.00204682902592</v>
+      <c r="AA4" s="2" t="n">
+        <v>273.3732952333632</v>
       </c>
     </row>
     <row r="5">
@@ -647,42 +797,72 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10.85365853658537</v>
+        <v>4137.18820861678</v>
       </c>
       <c r="D5" t="n">
-        <v>20.25727635767402</v>
+        <v>395.4992050783974</v>
       </c>
       <c r="E5" t="n">
-        <v>14.15751049576736</v>
+        <v>276.4085382506961</v>
       </c>
       <c r="F5" t="n">
         <v>1.430850174098779</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3323716035502757</v>
+        <v>0.3323716035502758</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5246760670731707</v>
+        <v>1.428571428571428</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6710175304878049</v>
+        <v>13.10081845238095</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6121379573170732</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>5.638685161564625</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>7</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4.674479166666666</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>13.10081845238095</v>
+      </c>
+      <c r="R5" t="n">
+        <v>8.668951955782312</v>
+      </c>
+      <c r="S5" t="n">
+        <v>7</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.428571428571428</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3.463541666666667</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.608418367346939</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AA5" s="2" t="n">
         <v>1.398547828295247</v>
       </c>
     </row>
@@ -694,43 +874,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10.85365853658537</v>
+        <v>4137.18820861678</v>
       </c>
       <c r="D6" t="n">
-        <v>20.25727635767402</v>
+        <v>395.4992050783974</v>
       </c>
       <c r="E6" t="n">
-        <v>14.15751049576736</v>
+        <v>276.4085382506961</v>
       </c>
       <c r="F6" t="n">
         <v>1.430850174098779</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3323716035502757</v>
+        <v>0.3323716035502758</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5246760670731707</v>
+        <v>1.428571428571428</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6710175304878049</v>
+        <v>13.10081845238095</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6121379573170732</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>5.638685161564625</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>7</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4.674479166666666</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>13.10081845238095</v>
+      </c>
+      <c r="R6" t="n">
+        <v>8.668951955782312</v>
+      </c>
+      <c r="S6" t="n">
+        <v>7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.428571428571428</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.463541666666667</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2.608418367346939</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
-        <v>0.3535823325185418</v>
+      <c r="AA6" s="2" t="n">
+        <v>0.3535823325185419</v>
       </c>
     </row>
     <row r="7">
@@ -741,43 +951,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10.93158834027365</v>
+        <v>4166.893424036281</v>
       </c>
       <c r="D7" t="n">
-        <v>18.66916173841895</v>
+        <v>364.4931577500843</v>
       </c>
       <c r="E7" t="n">
-        <v>14.09444256526668</v>
+        <v>275.1772119885399</v>
       </c>
       <c r="F7" t="n">
-        <v>1.324576098130045</v>
+        <v>1.324576098130044</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3941336328748378</v>
+        <v>0.3941336328748379</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5467797256097561</v>
+        <v>1.904761904761905</v>
       </c>
       <c r="J7" t="n">
-        <v>0.622141768292683</v>
+        <v>12.14657738095238</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5844607469512195</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>4.681299603174602</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4.821428571428571</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>12.14657738095238</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7.741505456349206</v>
+      </c>
+      <c r="S7" t="n">
+        <v>9</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.904761904761905</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.766741071428571</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.641162367724868</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>3</v>
+      <c r="AA7" s="2" t="n">
+        <v>13.9</v>
       </c>
     </row>
     <row r="8">
@@ -788,43 +1028,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10.93158834027365</v>
+        <v>4166.893424036281</v>
       </c>
       <c r="D8" t="n">
-        <v>18.66916173841895</v>
+        <v>364.4931577500843</v>
       </c>
       <c r="E8" t="n">
-        <v>14.09444256526668</v>
+        <v>275.1772119885399</v>
       </c>
       <c r="F8" t="n">
-        <v>1.324576098130045</v>
+        <v>1.324576098130044</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3941336328748378</v>
+        <v>0.3941336328748379</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5467797256097561</v>
+        <v>1.904761904761905</v>
       </c>
       <c r="J8" t="n">
-        <v>0.622141768292683</v>
+        <v>12.14657738095238</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5844607469512195</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>4.681299603174602</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>6</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.821428571428571</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>12.14657738095238</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7.741505456349206</v>
+      </c>
+      <c r="S8" t="n">
+        <v>9</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.904761904761905</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.766741071428571</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.641162367724868</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.5243140243902439</v>
+      <c r="AA8" s="2" t="n">
+        <v>1.802269345238095</v>
       </c>
     </row>
     <row r="9">
@@ -835,43 +1105,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10.8545508625818</v>
+        <v>4137.528344671202</v>
       </c>
       <c r="D9" t="n">
-        <v>19.33780113080653</v>
+        <v>377.547545887175</v>
       </c>
       <c r="E9" t="n">
-        <v>14.10873004285301</v>
+        <v>275.4561579795111</v>
       </c>
       <c r="F9" t="n">
         <v>1.370626631317706</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3647602819476933</v>
+        <v>0.3647602819476934</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5396341463414634</v>
+        <v>1.722470238095238</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6636814024390244</v>
+        <v>12.95758928571428</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6061674288617885</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>5.347310799319728</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>12.95758928571428</v>
+      </c>
+      <c r="R9" t="n">
+        <v>11.01888020833333</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.722470238095238</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4.427083333333333</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3.078683035714286</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.6631288109756098</v>
+      <c r="AA9" s="2" t="n">
+        <v>12.94680059523809</v>
       </c>
     </row>
     <row r="10">
@@ -882,43 +1182,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10.8545508625818</v>
+        <v>4137.528344671202</v>
       </c>
       <c r="D10" t="n">
-        <v>19.33780113080653</v>
+        <v>377.547545887175</v>
       </c>
       <c r="E10" t="n">
-        <v>14.10873004285301</v>
+        <v>275.4561579795111</v>
       </c>
       <c r="F10" t="n">
         <v>1.370626631317706</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3647602819476933</v>
+        <v>0.3647602819476934</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5396341463414634</v>
+        <v>1.722470238095238</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6636814024390244</v>
+        <v>12.95758928571428</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6061674288617885</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>5.347310799319728</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>12.95758928571428</v>
+      </c>
+      <c r="R10" t="n">
+        <v>11.01888020833333</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.722470238095238</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4.427083333333333</v>
+      </c>
+      <c r="V10" t="n">
+        <v>3.078683035714286</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.5937285632621951</v>
+      <c r="AA10" s="2" t="n">
+        <v>5.412754872855318</v>
       </c>
     </row>
     <row r="11">
@@ -929,35 +1259,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10.79684711481261</v>
+        <v>4115.532879818594</v>
       </c>
       <c r="D11" t="n">
-        <v>19.1643207160438</v>
+        <v>374.160547313236</v>
       </c>
       <c r="E11" t="n">
-        <v>14.05403150000223</v>
+        <v>274.3882340476626</v>
       </c>
       <c r="F11" t="n">
         <v>1.363617316215689</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3694196184097938</v>
+        <v>0.3694196184097939</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5072408536585366</v>
+        <v>2.189360119047619</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6719702743902439</v>
+        <v>13.11941964285714</v>
       </c>
       <c r="K11" t="n">
-        <v>0.57885543699187</v>
+        <v>5.539005265567766</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>5.003720238095238</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>13.11941964285714</v>
+      </c>
+      <c r="R11" t="n">
+        <v>9.649925595238095</v>
+      </c>
+      <c r="S11" t="n">
+        <v>8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.189360119047619</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.904389880952381</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.96968005952381</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="12">
@@ -968,35 +1336,73 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10.79684711481261</v>
+        <v>4115.532879818594</v>
       </c>
       <c r="D12" t="n">
-        <v>19.1643207160438</v>
+        <v>374.160547313236</v>
       </c>
       <c r="E12" t="n">
-        <v>14.05403150000223</v>
+        <v>274.3882340476626</v>
       </c>
       <c r="F12" t="n">
         <v>1.363617316215689</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3694196184097938</v>
+        <v>0.3694196184097939</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5072408536585366</v>
+        <v>2.189360119047619</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6719702743902439</v>
+        <v>13.11941964285714</v>
       </c>
       <c r="K12" t="n">
-        <v>0.57885543699187</v>
+        <v>5.539005265567766</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5.003720238095238</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>13.11941964285714</v>
+      </c>
+      <c r="R12" t="n">
+        <v>9.649925595238095</v>
+      </c>
+      <c r="S12" t="n">
+        <v>8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.189360119047619</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.904389880952381</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.96968005952381</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="n">
+        <v>14.39918154761904</v>
       </c>
     </row>
     <row r="13">
@@ -1007,17 +1413,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10.71118381915526</v>
+        <v>4082.879818594104</v>
       </c>
       <c r="D13" t="n">
-        <v>18.82775999569311</v>
+        <v>367.5895999159131</v>
       </c>
       <c r="E13" t="n">
-        <v>13.93279824605802</v>
+        <v>272.0212990897042</v>
       </c>
       <c r="F13" t="n">
         <v>1.351326536363219</v>
@@ -1026,16 +1432,54 @@
         <v>0.379708246624395</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5162919207317074</v>
+        <v>1.852678571428571</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6719702743902439</v>
+        <v>13.11941964285714</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5766006097560975</v>
+        <v>5.439417353479853</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>5.42782738095238</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>13.11941964285714</v>
+      </c>
+      <c r="R13" t="n">
+        <v>9.744791666666668</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.852678571428571</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4.229910714285714</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.748558407738095</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="n">
+        <v>13.93229166666667</v>
       </c>
     </row>
     <row r="14">
@@ -1046,17 +1490,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10.71118381915526</v>
+        <v>4082.879818594104</v>
       </c>
       <c r="D14" t="n">
-        <v>18.82775999569311</v>
+        <v>367.5895999159131</v>
       </c>
       <c r="E14" t="n">
-        <v>13.93279824605802</v>
+        <v>272.0212990897042</v>
       </c>
       <c r="F14" t="n">
         <v>1.351326536363219</v>
@@ -1065,16 +1509,54 @@
         <v>0.379708246624395</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5162919207317074</v>
+        <v>1.852678571428571</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6719702743902439</v>
+        <v>13.11941964285714</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5766006097560975</v>
+        <v>5.439417353479853</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>5.42782738095238</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>13.11941964285714</v>
+      </c>
+      <c r="R14" t="n">
+        <v>9.744791666666668</v>
+      </c>
+      <c r="S14" t="n">
+        <v>8</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.852678571428571</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4.229910714285714</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2.748558407738095</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="n">
+        <v>5.35</v>
       </c>
     </row>
     <row r="15">
@@ -1085,35 +1567,73 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10.63563355145747</v>
+        <v>4054.081632653061</v>
       </c>
       <c r="D15" t="n">
-        <v>18.32118552487071</v>
+        <v>357.699336437952</v>
       </c>
       <c r="E15" t="n">
-        <v>13.93871631854918</v>
+        <v>272.1368424097697</v>
       </c>
       <c r="F15" t="n">
         <v>1.314409814086645</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3981677531132445</v>
+        <v>0.3981677531132444</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5274390243902439</v>
+        <v>2.114955357142857</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5637385670731707</v>
+        <v>11.0063244047619</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5425876524390244</v>
+        <v>5.253834706959707</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>6.060267857142857</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>11.0063244047619</v>
+      </c>
+      <c r="R15" t="n">
+        <v>9.21688988095238</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.114955357142857</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4.229910714285714</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.776925223214286</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="n">
+        <v>5.992094494047619</v>
       </c>
     </row>
     <row r="16">
@@ -1124,35 +1644,73 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10.63563355145747</v>
+        <v>4054.081632653061</v>
       </c>
       <c r="D16" t="n">
-        <v>18.32118552487071</v>
+        <v>357.699336437952</v>
       </c>
       <c r="E16" t="n">
-        <v>13.93871631854918</v>
+        <v>272.1368424097697</v>
       </c>
       <c r="F16" t="n">
         <v>1.314409814086645</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3981677531132445</v>
+        <v>0.3981677531132444</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5274390243902439</v>
+        <v>2.114955357142857</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5637385670731707</v>
+        <v>11.0063244047619</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5425876524390244</v>
+        <v>5.253834706959707</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>6.060267857142857</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>11.0063244047619</v>
+      </c>
+      <c r="R16" t="n">
+        <v>9.21688988095238</v>
+      </c>
+      <c r="S16" t="n">
+        <v>8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.114955357142857</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4.229910714285714</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2.776925223214286</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="n">
+        <v>12.70535714285714</v>
       </c>
     </row>
     <row r="17">
@@ -1163,35 +1721,73 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10.47888161808447</v>
+        <v>3994.331065759637</v>
       </c>
       <c r="D17" t="n">
-        <v>20.15421793809751</v>
+        <v>393.4871121247609</v>
       </c>
       <c r="E17" t="n">
-        <v>13.77808735138033</v>
+        <v>269.0007530507587</v>
       </c>
       <c r="F17" t="n">
         <v>1.462773273539916</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3241849857176215</v>
+        <v>0.3241849857176216</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5045731707317074</v>
+        <v>1.945684523809524</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6894054878048781</v>
+        <v>13.45982142857143</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6076362423780488</v>
+        <v>5.521364795918367</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>6.417410714285714</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>13.45982142857143</v>
+      </c>
+      <c r="R17" t="n">
+        <v>10.77418154761905</v>
+      </c>
+      <c r="S17" t="n">
+        <v>9</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.945684523809524</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3.746279761904762</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.603133267195767</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="n">
+        <v>9.443553580286281</v>
       </c>
     </row>
     <row r="18">
@@ -1202,35 +1798,73 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10.47888161808447</v>
+        <v>3994.331065759637</v>
       </c>
       <c r="D18" t="n">
-        <v>20.15421793809751</v>
+        <v>393.4871121247609</v>
       </c>
       <c r="E18" t="n">
-        <v>13.77808735138033</v>
+        <v>269.0007530507587</v>
       </c>
       <c r="F18" t="n">
         <v>1.462773273539916</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3241849857176215</v>
+        <v>0.3241849857176216</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5045731707317074</v>
+        <v>1.945684523809524</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6894054878048781</v>
+        <v>13.45982142857143</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6076362423780488</v>
+        <v>5.521364795918367</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>6.417410714285714</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>13.45982142857143</v>
+      </c>
+      <c r="R18" t="n">
+        <v>10.77418154761905</v>
+      </c>
+      <c r="S18" t="n">
+        <v>9</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.945684523809524</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3.746279761904762</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.603133267195767</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="n">
+        <v>8.35</v>
       </c>
     </row>
     <row r="19">
@@ -1241,17 +1875,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10.39351576442594</v>
+        <v>3961.791383219954</v>
       </c>
       <c r="D19" t="n">
-        <v>20.55731334628128</v>
+        <v>401.3570700940631</v>
       </c>
       <c r="E19" t="n">
-        <v>13.70665000996939</v>
+        <v>267.6060240041642</v>
       </c>
       <c r="F19" t="n">
         <v>1.499805811874465</v>
@@ -1260,16 +1894,57 @@
         <v>0.3090577451675081</v>
       </c>
       <c r="H19" t="n">
+        <v>15</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.595982142857143</v>
+      </c>
+      <c r="J19" t="n">
+        <v>13.91555059523809</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.291418650793648</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>13.91555059523809</v>
+      </c>
+      <c r="O19" t="n">
         <v>4</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.5171493902439025</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.7127477134146342</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.6221179496951219</v>
+      <c r="P19" t="n">
+        <v>7.131696428571428</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>13.53050595238095</v>
+      </c>
+      <c r="R19" t="n">
+        <v>10.45014880952381</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.595982142857143</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.896205357142857</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.365513392857143</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="n">
+        <v>1.802269345238095</v>
       </c>
     </row>
     <row r="20">
@@ -1280,17 +1955,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10.39351576442594</v>
+        <v>3961.791383219954</v>
       </c>
       <c r="D20" t="n">
-        <v>20.55731334628128</v>
+        <v>401.3570700940631</v>
       </c>
       <c r="E20" t="n">
-        <v>13.70665000996939</v>
+        <v>267.6060240041642</v>
       </c>
       <c r="F20" t="n">
         <v>1.499805811874465</v>
@@ -1299,16 +1974,57 @@
         <v>0.3090577451675081</v>
       </c>
       <c r="H20" t="n">
+        <v>15</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.595982142857143</v>
+      </c>
+      <c r="J20" t="n">
+        <v>13.91555059523809</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.291418650793648</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>13.91555059523809</v>
+      </c>
+      <c r="O20" t="n">
         <v>4</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.5171493902439025</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.7127477134146342</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.6221179496951219</v>
+      <c r="P20" t="n">
+        <v>7.131696428571428</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>13.53050595238095</v>
+      </c>
+      <c r="R20" t="n">
+        <v>10.45014880952381</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.595982142857143</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.896205357142857</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.365513392857143</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="n">
+        <v>3.760974702380953</v>
       </c>
     </row>
     <row r="21">
@@ -1319,17 +2035,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10.27067221891731</v>
+        <v>3914.965986394558</v>
       </c>
       <c r="D21" t="n">
-        <v>22.2774818873987</v>
+        <v>434.9413130396888</v>
       </c>
       <c r="E21" t="n">
-        <v>13.75889719986334</v>
+        <v>268.6260881878081</v>
       </c>
       <c r="F21" t="n">
         <v>1.619132810122309</v>
@@ -1338,16 +2054,60 @@
         <v>0.2600617824116132</v>
       </c>
       <c r="H21" t="n">
+        <v>11</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.256324404761905</v>
+      </c>
+      <c r="J21" t="n">
+        <v>15.36644345238095</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7.549546807359307</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>15.36644345238095</v>
+      </c>
+      <c r="N21" t="n">
+        <v>13.93229166666667</v>
+      </c>
+      <c r="O21" t="n">
         <v>4</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.547827743902439</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.7870617378048781</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.6569169207317074</v>
+      <c r="P21" t="n">
+        <v>8.909970238095237</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>11.30766369047619</v>
+      </c>
+      <c r="R21" t="n">
+        <v>10.08510044642857</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.256324404761905</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3.048735119047619</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.681175595238095</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="n">
+        <v>2.68467383698271</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2117,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1380,6 +2148,38 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/measurements/36/Filled_2D_sections/sagittal/week36_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/36/Filled_2D_sections/sagittal/week36_sagittal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2185,4 +2391,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week36_sagittal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4079.580498866212</v>
+      </c>
+      <c r="D10" t="n">
+        <v>75.4587468166803</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3914.965986394558</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4166.893424036281</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>382.171620051066</v>
+      </c>
+      <c r="D11" t="n">
+        <v>18.57037401732814</v>
+      </c>
+      <c r="E11" t="n">
+        <v>357.699336437952</v>
+      </c>
+      <c r="F11" t="n">
+        <v>434.9413130396888</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.398547828295247</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.07786094488564886</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.314409814086645</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.619132810122309</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.3535823325185419</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.03608308290002129</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2600617824116132</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3981677531132444</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis0_s00_idx0173.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>8</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis0_s01_idx0173.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis0_s02_idx0173.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>15</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>15</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>8</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis0_s03_idx0174.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>14</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>14</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis0_s04_idx0174.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>14</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis0_s05_idx0175.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>15</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis0_s06_idx0175.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>15</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>15</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>9</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis0_s07_idx0176.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>14</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>14</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>10</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis0_s08_idx0176.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>14</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>14</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>10</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis0_s09_idx0177.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>13</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>8</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>13</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>8</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis0_s10_idx0177.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>13</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>8</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>13</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>8</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis0_s11_idx0178.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>13</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>13</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>8</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis0_s12_idx0178.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>13</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>8</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>13</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>8</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis0_s13_idx0179.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>13</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>13</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>8</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis0_s14_idx0179.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>13</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>8</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>13</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>8</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis0_s15_idx0180.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>14</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>14</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>9</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis0_s16_idx0180.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>14</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>14</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>9</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis0_s17_idx0181.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>15</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" t="n">
+        <v>10</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>15</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>10</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis0_s18_idx0181.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>15</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>10</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>15</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>10</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis0_s19_idx0182.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>11</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>11</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4</v>
+      </c>
+      <c r="J36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.071152846727595</v>
+      </c>
+      <c r="E40" t="n">
+        <v>11</v>
+      </c>
+      <c r="F40" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.523148363780597</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.136708081768532</v>
+      </c>
+      <c r="E42" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.22581873821025</v>
+      </c>
+      <c r="E43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" t="n">
+        <v>14.28245907738095</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.7226993402762639</v>
+      </c>
+      <c r="E48" t="n">
+        <v>13.91555059523809</v>
+      </c>
+      <c r="F48" t="n">
+        <v>15.36644345238095</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>107</v>
+      </c>
+      <c r="C49" t="n">
+        <v>9.252353832888295</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.425159218311572</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.674479166666666</v>
+      </c>
+      <c r="F49" t="n">
+        <v>13.53050595238095</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>167</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.68594507413744</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.5509818111322142</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.42671130952381</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.427083333333333</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>